--- a/docs/requirements/WBS.xlsx
+++ b/docs/requirements/WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bini/Desktop/Bini/단위프로젝트/SKN30-FINAL-5Team/docs/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE654C34-A4D2-AF49-BFE7-8CF725BFA125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3559EEED-CDFF-714C-85CB-949869BC800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t>작업 완료 비율</t>
-  </si>
-  <si>
-    <t>헬스·웰니스 운동 지속 관리 서비스</t>
   </si>
   <si>
     <t>30기 5팀</t>
@@ -1485,6 +1482,28 @@
     </r>
     <phoneticPr fontId="25" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF999999"/>
+        <rFont val="Batang"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>헬끼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF999999"/>
+        <rFont val="Roboto"/>
+        <family val="1"/>
+      </rPr>
+      <t>(helkki)</t>
+    </r>
+    <phoneticPr fontId="25" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1496,7 +1515,7 @@
     <numFmt numFmtId="178" formatCode=";;;"/>
     <numFmt numFmtId="179" formatCode="0&quot;일&quot;"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="48">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1765,6 +1784,19 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF999999"/>
+      <name val="Roboto"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF999999"/>
+      <name val="Roboto"/>
+      <family val="1"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -2245,7 +2277,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="193">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2651,112 +2683,6 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2768,6 +2694,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2789,6 +2718,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="19" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2796,6 +2828,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3175,40 +3210,40 @@
     </row>
     <row r="2" spans="1:69" ht="41" customHeight="1" thickBot="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
       <c r="H2" s="135"/>
-      <c r="I2" s="179"/>
-      <c r="J2" s="178"/>
-      <c r="K2" s="178"/>
-      <c r="L2" s="178"/>
-      <c r="M2" s="178"/>
-      <c r="N2" s="178"/>
-      <c r="O2" s="180"/>
-      <c r="P2" s="181"/>
-      <c r="Q2" s="181"/>
-      <c r="R2" s="181"/>
-      <c r="S2" s="181"/>
-      <c r="T2" s="181"/>
-      <c r="U2" s="181"/>
-      <c r="V2" s="181"/>
-      <c r="W2" s="181"/>
-      <c r="X2" s="181"/>
-      <c r="Y2" s="181"/>
-      <c r="Z2" s="181"/>
-      <c r="AA2" s="181"/>
-      <c r="AB2" s="181"/>
-      <c r="AC2" s="181"/>
-      <c r="AD2" s="181"/>
-      <c r="AE2" s="181"/>
-      <c r="AF2" s="181"/>
-      <c r="AG2" s="181"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="144"/>
+      <c r="P2" s="145"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
+      <c r="T2" s="145"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="145"/>
+      <c r="W2" s="145"/>
+      <c r="X2" s="145"/>
+      <c r="Y2" s="145"/>
+      <c r="Z2" s="145"/>
+      <c r="AA2" s="145"/>
+      <c r="AB2" s="145"/>
+      <c r="AC2" s="145"/>
+      <c r="AD2" s="145"/>
+      <c r="AE2" s="145"/>
+      <c r="AF2" s="145"/>
+      <c r="AG2" s="145"/>
       <c r="AH2" s="10"/>
       <c r="AI2" s="10"/>
       <c r="AJ2" s="10"/>
@@ -3246,49 +3281,49 @@
       <c r="BP2" s="1"/>
       <c r="BQ2" s="1"/>
     </row>
-    <row r="3" spans="1:69" s="188" customFormat="1" ht="21" customHeight="1" thickTop="1"/>
+    <row r="3" spans="1:69" s="153" customFormat="1" ht="21" customHeight="1" thickTop="1"/>
     <row r="4" spans="1:69" ht="21" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="150" t="s">
+      <c r="B4" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="150"/>
-      <c r="D4" s="182" t="s">
+      <c r="C4" s="146"/>
+      <c r="D4" s="192" t="s">
+        <v>413</v>
+      </c>
+      <c r="E4" s="147"/>
+      <c r="F4" s="147"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="150"/>
+      <c r="P4" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="182"/>
-      <c r="F4" s="182"/>
-      <c r="G4" s="182"/>
-      <c r="H4" s="183" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
-      <c r="M4" s="184"/>
-      <c r="N4" s="184"/>
-      <c r="O4" s="185"/>
-      <c r="P4" s="186" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="187"/>
-      <c r="R4" s="187"/>
-      <c r="S4" s="187"/>
-      <c r="T4" s="187"/>
-      <c r="U4" s="187"/>
-      <c r="V4" s="187"/>
-      <c r="W4" s="187"/>
-      <c r="X4" s="187"/>
-      <c r="Y4" s="187"/>
-      <c r="Z4" s="187"/>
-      <c r="AA4" s="187"/>
-      <c r="AB4" s="187"/>
-      <c r="AC4" s="187"/>
-      <c r="AD4" s="187"/>
-      <c r="AE4" s="187"/>
-      <c r="AF4" s="187"/>
-      <c r="AG4" s="187"/>
+      <c r="Q4" s="152"/>
+      <c r="R4" s="152"/>
+      <c r="S4" s="152"/>
+      <c r="T4" s="152"/>
+      <c r="U4" s="152"/>
+      <c r="V4" s="152"/>
+      <c r="W4" s="152"/>
+      <c r="X4" s="152"/>
+      <c r="Y4" s="152"/>
+      <c r="Z4" s="152"/>
+      <c r="AA4" s="152"/>
+      <c r="AB4" s="152"/>
+      <c r="AC4" s="152"/>
+      <c r="AD4" s="152"/>
+      <c r="AE4" s="152"/>
+      <c r="AF4" s="152"/>
+      <c r="AG4" s="152"/>
       <c r="AH4" s="9"/>
       <c r="AI4" s="9"/>
       <c r="AJ4" s="9"/>
@@ -3328,46 +3363,46 @@
     </row>
     <row r="5" spans="1:69" ht="21" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="150" t="s">
+      <c r="B5" s="146" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="150"/>
-      <c r="D5" s="151" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="151"/>
-      <c r="F5" s="151"/>
-      <c r="G5" s="151"/>
-      <c r="H5" s="161" t="s">
+      <c r="C5" s="146"/>
+      <c r="D5" s="176" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
+      <c r="H5" s="186" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="163"/>
-      <c r="P5" s="141">
+      <c r="I5" s="187"/>
+      <c r="J5" s="187"/>
+      <c r="K5" s="187"/>
+      <c r="L5" s="187"/>
+      <c r="M5" s="187"/>
+      <c r="N5" s="187"/>
+      <c r="O5" s="188"/>
+      <c r="P5" s="170">
         <v>46244.125</v>
       </c>
-      <c r="Q5" s="142"/>
-      <c r="R5" s="142"/>
-      <c r="S5" s="142"/>
-      <c r="T5" s="142"/>
-      <c r="U5" s="142"/>
-      <c r="V5" s="142"/>
-      <c r="W5" s="142"/>
-      <c r="X5" s="142"/>
-      <c r="Y5" s="142"/>
-      <c r="Z5" s="142"/>
-      <c r="AA5" s="142"/>
-      <c r="AB5" s="142"/>
-      <c r="AC5" s="142"/>
-      <c r="AD5" s="142"/>
-      <c r="AE5" s="142"/>
-      <c r="AF5" s="142"/>
-      <c r="AG5" s="142"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="171"/>
+      <c r="S5" s="171"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="171"/>
+      <c r="Y5" s="171"/>
+      <c r="Z5" s="171"/>
+      <c r="AA5" s="171"/>
+      <c r="AB5" s="171"/>
+      <c r="AC5" s="171"/>
+      <c r="AD5" s="171"/>
+      <c r="AE5" s="171"/>
+      <c r="AF5" s="171"/>
+      <c r="AG5" s="171"/>
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
@@ -3621,373 +3656,373 @@
     </row>
     <row r="8" spans="1:69" ht="22" customHeight="1">
       <c r="A8" s="15"/>
-      <c r="B8" s="175" t="s">
+      <c r="B8" s="168" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="168" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="175" t="s">
+      <c r="D8" s="168" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="175" t="s">
+      <c r="E8" s="168" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="175" t="s">
+      <c r="F8" s="168" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="175" t="s">
+      <c r="G8" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="175" t="s">
+      <c r="H8" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="152" t="s">
+      <c r="I8" s="177" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="178" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="178" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" s="178" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="179" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="153" t="s">
+      <c r="O8" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="K8" s="153" t="s">
+      <c r="P8" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="153" t="s">
+      <c r="Q8" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="154" t="s">
+      <c r="R8" s="181" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="155" t="s">
+      <c r="S8" s="181" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" s="181" t="s">
+        <v>15</v>
+      </c>
+      <c r="U8" s="181" t="s">
+        <v>15</v>
+      </c>
+      <c r="V8" s="181" t="s">
+        <v>15</v>
+      </c>
+      <c r="W8" s="182" t="s">
+        <v>15</v>
+      </c>
+      <c r="X8" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="O8" s="156" t="s">
+      <c r="Y8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="P8" s="156" t="s">
+      <c r="Z8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="Q8" s="156" t="s">
+      <c r="AA8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="R8" s="156" t="s">
+      <c r="AB8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="156" t="s">
+      <c r="AC8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="T8" s="156" t="s">
+      <c r="AD8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="U8" s="156" t="s">
+      <c r="AE8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="V8" s="156" t="s">
+      <c r="AF8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="W8" s="157" t="s">
+      <c r="AG8" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="X8" s="158" t="s">
+      <c r="AH8" s="184" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI8" s="184" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ8" s="184" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK8" s="184" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL8" s="185" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM8" s="157" t="s">
         <v>17</v>
       </c>
-      <c r="Y8" s="159" t="s">
+      <c r="AN8" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="Z8" s="159" t="s">
+      <c r="AO8" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="AA8" s="159" t="s">
+      <c r="AP8" s="158" t="s">
         <v>17</v>
       </c>
-      <c r="AB8" s="159" t="s">
+      <c r="AQ8" s="159" t="s">
         <v>17</v>
-      </c>
-      <c r="AC8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AK8" s="159" t="s">
-        <v>17</v>
-      </c>
-      <c r="AL8" s="160" t="s">
-        <v>17</v>
-      </c>
-      <c r="AM8" s="164" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN8" s="165" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO8" s="165" t="s">
-        <v>18</v>
-      </c>
-      <c r="AP8" s="165" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ8" s="166" t="s">
-        <v>18</v>
       </c>
       <c r="AR8" s="12"/>
     </row>
     <row r="9" spans="1:69" ht="21" customHeight="1">
       <c r="A9" s="16"/>
-      <c r="B9" s="176"/>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="176"/>
-      <c r="F9" s="176"/>
-      <c r="G9" s="176"/>
-      <c r="H9" s="176"/>
-      <c r="I9" s="167" t="s">
+      <c r="B9" s="169"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
+      <c r="I9" s="160" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="161" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="161" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" s="161" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="162" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="168" t="s">
+      <c r="O9" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="K9" s="168" t="s">
+      <c r="P9" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="L9" s="168" t="s">
+      <c r="Q9" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="168" t="s">
+      <c r="R9" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="169" t="s">
+      <c r="S9" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="O9" s="170" t="s">
+      <c r="T9" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="170" t="s">
+      <c r="U9" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="170" t="s">
+      <c r="V9" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="R9" s="170" t="s">
+      <c r="W9" s="163" t="s">
         <v>20</v>
       </c>
-      <c r="S9" s="169" t="s">
+      <c r="X9" s="164" t="s">
         <v>21</v>
       </c>
-      <c r="T9" s="170" t="s">
+      <c r="Y9" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="U9" s="170" t="s">
+      <c r="Z9" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="V9" s="170" t="s">
+      <c r="AA9" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="W9" s="170" t="s">
+      <c r="AB9" s="165" t="s">
         <v>21</v>
       </c>
-      <c r="X9" s="171" t="s">
+      <c r="AC9" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="Y9" s="172" t="s">
+      <c r="AD9" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="Z9" s="172" t="s">
+      <c r="AE9" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="AA9" s="172" t="s">
+      <c r="AF9" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="AB9" s="172" t="s">
+      <c r="AG9" s="165" t="s">
         <v>22</v>
       </c>
-      <c r="AC9" s="171" t="s">
+      <c r="AH9" s="164" t="s">
         <v>23</v>
       </c>
-      <c r="AD9" s="172" t="s">
+      <c r="AI9" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="AE9" s="172" t="s">
+      <c r="AJ9" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="AF9" s="172" t="s">
+      <c r="AK9" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="AG9" s="172" t="s">
+      <c r="AL9" s="165" t="s">
         <v>23</v>
       </c>
-      <c r="AH9" s="171" t="s">
+      <c r="AM9" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="AI9" s="172" t="s">
+      <c r="AN9" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="AJ9" s="172" t="s">
+      <c r="AO9" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="AK9" s="172" t="s">
+      <c r="AP9" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="AL9" s="172" t="s">
+      <c r="AQ9" s="167" t="s">
         <v>24</v>
-      </c>
-      <c r="AM9" s="173" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN9" s="174" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO9" s="174" t="s">
-        <v>25</v>
-      </c>
-      <c r="AP9" s="174" t="s">
-        <v>25</v>
-      </c>
-      <c r="AQ9" s="174" t="s">
-        <v>25</v>
       </c>
       <c r="AR9" s="16"/>
     </row>
     <row r="10" spans="1:69" ht="28" customHeight="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="176"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="176"/>
-      <c r="E10" s="176"/>
-      <c r="F10" s="176"/>
-      <c r="G10" s="176"/>
-      <c r="H10" s="176"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
       <c r="I10" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="K10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="L10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="M10" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="22" t="s">
+      <c r="N10" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="N10" s="32" t="s">
+      <c r="O10" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="32" t="s">
+      <c r="P10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="P10" s="32" t="s">
+      <c r="Q10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="Q10" s="32" t="s">
+      <c r="R10" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="R10" s="32" t="s">
+      <c r="S10" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="T10" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="S10" s="86" t="s">
-        <v>195</v>
-      </c>
-      <c r="T10" s="32" t="s">
+      <c r="U10" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="32" t="s">
+      <c r="V10" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="V10" s="32" t="s">
+      <c r="W10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="W10" s="32" t="s">
+      <c r="X10" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="X10" s="36" t="s">
+      <c r="Y10" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="Y10" s="36" t="s">
+      <c r="Z10" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="Z10" s="36" t="s">
+      <c r="AA10" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="AA10" s="36" t="s">
+      <c r="AB10" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="AB10" s="36" t="s">
+      <c r="AC10" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="AC10" s="36" t="s">
+      <c r="AD10" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="AD10" s="36" t="s">
+      <c r="AE10" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="AE10" s="36" t="s">
+      <c r="AF10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="AF10" s="36" t="s">
+      <c r="AG10" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="AG10" s="36" t="s">
+      <c r="AH10" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="AH10" s="36" t="s">
+      <c r="AI10" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="AI10" s="36" t="s">
+      <c r="AJ10" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="AJ10" s="36" t="s">
+      <c r="AK10" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="AK10" s="36" t="s">
+      <c r="AL10" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="AL10" s="36" t="s">
+      <c r="AM10" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="AM10" s="40" t="s">
+      <c r="AN10" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="AN10" s="40" t="s">
+      <c r="AO10" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="AO10" s="40" t="s">
+      <c r="AP10" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="AP10" s="40" t="s">
+      <c r="AQ10" s="40" t="s">
         <v>58</v>
-      </c>
-      <c r="AQ10" s="40" t="s">
-        <v>59</v>
       </c>
       <c r="AR10" s="17"/>
     </row>
     <row r="11" spans="1:69" ht="22" customHeight="1">
       <c r="A11" s="12"/>
       <c r="B11" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="48" t="s">
         <v>60</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>61</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="50"/>
@@ -4034,13 +4069,13 @@
     <row r="12" spans="1:69" ht="26" customHeight="1">
       <c r="A12" s="18"/>
       <c r="B12" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="D12" s="58" t="s">
         <v>63</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>64</v>
       </c>
       <c r="E12" s="59">
         <v>46237.125</v>
@@ -4095,13 +4130,13 @@
     <row r="13" spans="1:69" ht="26" customHeight="1">
       <c r="A13" s="18"/>
       <c r="B13" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="D13" s="58" t="s">
         <v>66</v>
-      </c>
-      <c r="D13" s="58" t="s">
-        <v>67</v>
       </c>
       <c r="E13" s="59">
         <v>46238.125</v>
@@ -4156,13 +4191,13 @@
     <row r="14" spans="1:69" ht="26" customHeight="1">
       <c r="A14" s="18"/>
       <c r="B14" s="56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="57" t="s">
-        <v>69</v>
-      </c>
       <c r="D14" s="58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" s="59">
         <v>46237.125</v>
@@ -4217,13 +4252,13 @@
     <row r="15" spans="1:69" ht="26" customHeight="1">
       <c r="A15" s="18"/>
       <c r="B15" s="56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="57" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="D15" s="58" t="s">
         <v>71</v>
-      </c>
-      <c r="D15" s="58" t="s">
-        <v>72</v>
       </c>
       <c r="E15" s="59">
         <v>46240.125</v>
@@ -4278,13 +4313,13 @@
     <row r="16" spans="1:69" ht="26" customHeight="1">
       <c r="A16" s="18"/>
       <c r="B16" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="57" t="s">
-        <v>74</v>
-      </c>
       <c r="D16" s="58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" s="59">
         <v>46241.125</v>
@@ -4339,13 +4374,13 @@
     <row r="17" spans="1:44" ht="26" customHeight="1">
       <c r="A17" s="18"/>
       <c r="B17" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="57" t="s">
-        <v>76</v>
-      </c>
       <c r="D17" s="58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" s="59">
         <v>46244.125</v>
@@ -4400,13 +4435,13 @@
     <row r="18" spans="1:44" ht="26" customHeight="1">
       <c r="A18" s="18"/>
       <c r="B18" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="57" t="s">
-        <v>78</v>
-      </c>
       <c r="D18" s="58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" s="59">
         <v>46252.125</v>
@@ -4461,10 +4496,10 @@
     <row r="19" spans="1:44" ht="22" customHeight="1">
       <c r="A19" s="12"/>
       <c r="B19" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="48" t="s">
         <v>79</v>
-      </c>
-      <c r="C19" s="48" t="s">
-        <v>80</v>
       </c>
       <c r="D19" s="49"/>
       <c r="E19" s="50"/>
@@ -4511,13 +4546,13 @@
     <row r="20" spans="1:44" ht="26" customHeight="1">
       <c r="A20" s="18"/>
       <c r="B20" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="D20" s="58" t="s">
         <v>82</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>83</v>
       </c>
       <c r="E20" s="59">
         <v>46244.125</v>
@@ -4572,13 +4607,13 @@
     <row r="21" spans="1:44" ht="26" customHeight="1">
       <c r="A21" s="18"/>
       <c r="B21" s="56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="57" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="57" t="s">
-        <v>85</v>
-      </c>
       <c r="D21" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="59">
         <v>46244.125</v>
@@ -4633,13 +4668,13 @@
     <row r="22" spans="1:44" ht="26" customHeight="1">
       <c r="A22" s="18"/>
       <c r="B22" s="56" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="D22" s="58" t="s">
         <v>87</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>88</v>
       </c>
       <c r="E22" s="59">
         <v>46246.125</v>
@@ -4694,13 +4729,13 @@
     <row r="23" spans="1:44" ht="26" customHeight="1">
       <c r="A23" s="18"/>
       <c r="B23" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="57" t="s">
-        <v>90</v>
-      </c>
       <c r="D23" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="59">
         <v>46244.125</v>
@@ -4755,13 +4790,13 @@
     <row r="24" spans="1:44" ht="26" customHeight="1">
       <c r="A24" s="12"/>
       <c r="B24" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="D24" s="64" t="s">
         <v>92</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>93</v>
       </c>
       <c r="E24" s="65">
         <v>46246.125</v>
@@ -4816,13 +4851,13 @@
     <row r="25" spans="1:44" ht="26" customHeight="1">
       <c r="A25" s="18"/>
       <c r="B25" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="57" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="57" t="s">
-        <v>95</v>
-      </c>
       <c r="D25" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="59">
         <v>46244.125</v>
@@ -4877,13 +4912,13 @@
     <row r="26" spans="1:44" ht="26" customHeight="1">
       <c r="A26" s="18"/>
       <c r="B26" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="D26" s="58" t="s">
         <v>97</v>
-      </c>
-      <c r="D26" s="58" t="s">
-        <v>98</v>
       </c>
       <c r="E26" s="59">
         <v>46251.125</v>
@@ -4938,13 +4973,13 @@
     <row r="27" spans="1:44" ht="26" customHeight="1">
       <c r="A27" s="18"/>
       <c r="B27" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>100</v>
-      </c>
       <c r="D27" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="59">
         <v>46251.125</v>
@@ -4999,13 +5034,13 @@
     <row r="28" spans="1:44" ht="26" customHeight="1">
       <c r="A28" s="18"/>
       <c r="B28" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="57" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="57" t="s">
-        <v>102</v>
-      </c>
       <c r="D28" s="58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E28" s="59">
         <v>46254.125</v>
@@ -5060,13 +5095,13 @@
     <row r="29" spans="1:44" ht="26" customHeight="1">
       <c r="A29" s="18"/>
       <c r="B29" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="57" t="s">
-        <v>104</v>
-      </c>
       <c r="D29" s="58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E29" s="59">
         <v>46251.125</v>
@@ -5121,13 +5156,13 @@
     <row r="30" spans="1:44" ht="26" customHeight="1">
       <c r="A30" s="18"/>
       <c r="B30" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="C30" s="57" t="s">
-        <v>106</v>
-      </c>
       <c r="D30" s="58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E30" s="59">
         <v>46251.125</v>
@@ -5182,13 +5217,13 @@
     <row r="31" spans="1:44" ht="26" customHeight="1">
       <c r="A31" s="12"/>
       <c r="B31" s="102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="103" t="s">
-        <v>108</v>
-      </c>
       <c r="D31" s="104" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31" s="105">
         <v>46261.125</v>
@@ -5243,10 +5278,10 @@
     <row r="32" spans="1:44" ht="22" customHeight="1">
       <c r="A32" s="18"/>
       <c r="B32" s="115" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="116" t="s">
         <v>109</v>
-      </c>
-      <c r="C32" s="116" t="s">
-        <v>110</v>
       </c>
       <c r="D32" s="117"/>
       <c r="E32" s="118"/>
@@ -5293,13 +5328,13 @@
     <row r="33" spans="1:69" ht="26" customHeight="1">
       <c r="A33" s="18"/>
       <c r="B33" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="D33" s="58" t="s">
         <v>112</v>
-      </c>
-      <c r="D33" s="58" t="s">
-        <v>113</v>
       </c>
       <c r="E33" s="59">
         <v>46251.125</v>
@@ -5354,13 +5389,13 @@
     <row r="34" spans="1:69" ht="26" customHeight="1">
       <c r="A34" s="18"/>
       <c r="B34" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C34" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="57" t="s">
-        <v>115</v>
-      </c>
       <c r="D34" s="58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E34" s="59">
         <v>46251.125</v>
@@ -5415,13 +5450,13 @@
     <row r="35" spans="1:69" ht="26" customHeight="1">
       <c r="A35" s="18"/>
       <c r="B35" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="57" t="s">
-        <v>117</v>
-      </c>
       <c r="D35" s="58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E35" s="59">
         <v>46254.125</v>
@@ -5476,13 +5511,13 @@
     <row r="36" spans="1:69" ht="26" customHeight="1">
       <c r="A36" s="12"/>
       <c r="B36" s="68" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="C36" s="63" t="s">
-        <v>119</v>
-      </c>
       <c r="D36" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E36" s="69">
         <v>46254.125</v>
@@ -5537,13 +5572,13 @@
     <row r="37" spans="1:69" ht="26" customHeight="1">
       <c r="A37" s="12"/>
       <c r="B37" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="63" t="s">
-        <v>121</v>
-      </c>
       <c r="D37" s="64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E37" s="69">
         <v>46258.125</v>
@@ -5598,13 +5633,13 @@
     <row r="38" spans="1:69" ht="26" customHeight="1">
       <c r="A38" s="12"/>
       <c r="B38" s="68" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="63" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="63" t="s">
-        <v>123</v>
-      </c>
       <c r="D38" s="64" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E38" s="69">
         <v>46258.125</v>
@@ -5683,13 +5718,13 @@
     </row>
     <row r="39" spans="1:69" ht="26" customHeight="1">
       <c r="B39" s="72" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="73" t="s">
         <v>124</v>
       </c>
-      <c r="C39" s="73" t="s">
+      <c r="D39" s="74" t="s">
         <v>125</v>
-      </c>
-      <c r="D39" s="74" t="s">
-        <v>126</v>
       </c>
       <c r="E39" s="75">
         <v>46251.125</v>
@@ -5742,13 +5777,13 @@
     </row>
     <row r="40" spans="1:69" ht="26" customHeight="1">
       <c r="B40" s="72" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="C40" s="73" t="s">
-        <v>128</v>
-      </c>
       <c r="D40" s="74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E40" s="75">
         <v>46260.125</v>
@@ -5801,13 +5836,13 @@
     </row>
     <row r="41" spans="1:69" ht="26" customHeight="1">
       <c r="B41" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="C41" s="73" t="s">
-        <v>130</v>
-      </c>
       <c r="D41" s="74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41" s="75">
         <v>46261.125</v>
@@ -5860,10 +5895,10 @@
     </row>
     <row r="42" spans="1:69" ht="22" customHeight="1">
       <c r="B42" s="83" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="84" t="s">
         <v>131</v>
-      </c>
-      <c r="C42" s="84" t="s">
-        <v>132</v>
       </c>
       <c r="D42" s="78"/>
       <c r="E42" s="79"/>
@@ -5908,13 +5943,13 @@
     </row>
     <row r="43" spans="1:69" ht="26" customHeight="1">
       <c r="B43" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="C43" s="73" t="s">
+      <c r="D43" s="74" t="s">
         <v>134</v>
-      </c>
-      <c r="D43" s="74" t="s">
-        <v>135</v>
       </c>
       <c r="E43" s="75">
         <v>46258.125</v>
@@ -5967,13 +6002,13 @@
     </row>
     <row r="44" spans="1:69" ht="26" customHeight="1">
       <c r="B44" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="73" t="s">
         <v>136</v>
       </c>
-      <c r="C44" s="73" t="s">
+      <c r="D44" s="74" t="s">
         <v>137</v>
-      </c>
-      <c r="D44" s="74" t="s">
-        <v>138</v>
       </c>
       <c r="E44" s="75">
         <v>46258.125</v>
@@ -6026,13 +6061,13 @@
     </row>
     <row r="45" spans="1:69" ht="26" customHeight="1">
       <c r="B45" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="73" t="s">
         <v>139</v>
       </c>
-      <c r="C45" s="73" t="s">
-        <v>140</v>
-      </c>
       <c r="D45" s="74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E45" s="75">
         <v>46261.125</v>
@@ -6085,13 +6120,13 @@
     </row>
     <row r="46" spans="1:69" ht="26" customHeight="1">
       <c r="B46" s="72" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="73" t="s">
         <v>141</v>
       </c>
-      <c r="C46" s="73" t="s">
+      <c r="D46" s="74" t="s">
         <v>142</v>
-      </c>
-      <c r="D46" s="74" t="s">
-        <v>143</v>
       </c>
       <c r="E46" s="75">
         <v>46258.125</v>
@@ -6144,13 +6179,13 @@
     </row>
     <row r="47" spans="1:69" ht="26" customHeight="1">
       <c r="B47" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="D47" s="74" t="s">
         <v>145</v>
-      </c>
-      <c r="D47" s="74" t="s">
-        <v>146</v>
       </c>
       <c r="E47" s="75">
         <v>46259.125</v>
@@ -6203,13 +6238,13 @@
     </row>
     <row r="48" spans="1:69" ht="26" customHeight="1">
       <c r="B48" s="72" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="C48" s="73" t="s">
+      <c r="D48" s="74" t="s">
         <v>148</v>
-      </c>
-      <c r="D48" s="74" t="s">
-        <v>149</v>
       </c>
       <c r="E48" s="75">
         <v>46261.125</v>
@@ -6262,13 +6297,13 @@
     </row>
     <row r="49" spans="2:43" ht="26" customHeight="1">
       <c r="B49" s="72" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="73" t="s">
         <v>150</v>
       </c>
-      <c r="C49" s="73" t="s">
-        <v>151</v>
-      </c>
       <c r="D49" s="74" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E49" s="75">
         <v>46265.125</v>
@@ -6321,13 +6356,13 @@
     </row>
     <row r="50" spans="2:43" ht="26" customHeight="1">
       <c r="B50" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="C50" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="C50" s="73" t="s">
-        <v>153</v>
-      </c>
       <c r="D50" s="74" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E50" s="75">
         <v>46266.125</v>
@@ -6380,13 +6415,13 @@
     </row>
     <row r="51" spans="2:43" ht="26" customHeight="1">
       <c r="B51" s="72" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="73" t="s">
         <v>154</v>
       </c>
-      <c r="C51" s="73" t="s">
-        <v>155</v>
-      </c>
       <c r="D51" s="74" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" s="75">
         <v>46266.125</v>
@@ -6439,13 +6474,13 @@
     </row>
     <row r="52" spans="2:43" ht="26" customHeight="1">
       <c r="B52" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="C52" s="73" t="s">
-        <v>157</v>
-      </c>
       <c r="D52" s="74" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E52" s="75">
         <v>46265.125</v>
@@ -6498,13 +6533,13 @@
     </row>
     <row r="53" spans="2:43" ht="26" customHeight="1">
       <c r="B53" s="72" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="C53" s="73" t="s">
-        <v>159</v>
-      </c>
       <c r="D53" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E53" s="75">
         <v>46268.125</v>
@@ -6557,13 +6592,13 @@
     </row>
     <row r="54" spans="2:43" ht="26" customHeight="1">
       <c r="B54" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="C54" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="73" t="s">
+      <c r="D54" s="74" t="s">
         <v>161</v>
-      </c>
-      <c r="D54" s="74" t="s">
-        <v>162</v>
       </c>
       <c r="E54" s="75">
         <v>46274.125</v>
@@ -6616,10 +6651,10 @@
     </row>
     <row r="55" spans="2:43" ht="22" customHeight="1">
       <c r="B55" s="83" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="84" t="s">
         <v>163</v>
-      </c>
-      <c r="C55" s="84" t="s">
-        <v>164</v>
       </c>
       <c r="D55" s="78"/>
       <c r="E55" s="79"/>
@@ -6664,13 +6699,13 @@
     </row>
     <row r="56" spans="2:43" ht="26" customHeight="1">
       <c r="B56" s="72" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" s="73" t="s">
         <v>165</v>
       </c>
-      <c r="C56" s="73" t="s">
-        <v>166</v>
-      </c>
       <c r="D56" s="74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E56" s="75">
         <v>46272.125</v>
@@ -6723,13 +6758,13 @@
     </row>
     <row r="57" spans="2:43" ht="26" customHeight="1">
       <c r="B57" s="72" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="C57" s="73" t="s">
-        <v>168</v>
-      </c>
       <c r="D57" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E57" s="75">
         <v>46274.125</v>
@@ -6782,13 +6817,13 @@
     </row>
     <row r="58" spans="2:43" ht="26" customHeight="1">
       <c r="B58" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="73" t="s">
-        <v>170</v>
-      </c>
       <c r="D58" s="74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E58" s="75">
         <v>46274.125</v>
@@ -6841,13 +6876,13 @@
     </row>
     <row r="59" spans="2:43" ht="26" customHeight="1">
       <c r="B59" s="72" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="C59" s="73" t="s">
-        <v>172</v>
-      </c>
       <c r="D59" s="74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E59" s="75">
         <v>46275.125</v>
@@ -6900,13 +6935,13 @@
     </row>
     <row r="60" spans="2:43" ht="26" customHeight="1">
       <c r="B60" s="72" t="s">
+        <v>172</v>
+      </c>
+      <c r="C60" s="73" t="s">
         <v>173</v>
       </c>
-      <c r="C60" s="73" t="s">
-        <v>174</v>
-      </c>
       <c r="D60" s="74" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E60" s="75">
         <v>46275.125</v>
@@ -6959,13 +6994,13 @@
     </row>
     <row r="61" spans="2:43" ht="26" customHeight="1">
       <c r="B61" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="C61" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="73" t="s">
-        <v>176</v>
-      </c>
       <c r="D61" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E61" s="75">
         <v>46276.125</v>
@@ -7018,13 +7053,13 @@
     </row>
     <row r="62" spans="2:43" ht="26" customHeight="1">
       <c r="B62" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="C62" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="C62" s="73" t="s">
-        <v>178</v>
-      </c>
       <c r="D62" s="74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E62" s="75">
         <v>46279.125</v>
@@ -7077,13 +7112,13 @@
     </row>
     <row r="63" spans="2:43" ht="26" customHeight="1">
       <c r="B63" s="72" t="s">
+        <v>178</v>
+      </c>
+      <c r="C63" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="C63" s="73" t="s">
-        <v>180</v>
-      </c>
       <c r="D63" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E63" s="75">
         <v>46279.125</v>
@@ -7136,13 +7171,13 @@
     </row>
     <row r="64" spans="2:43" ht="26" customHeight="1">
       <c r="B64" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="C64" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="C64" s="73" t="s">
-        <v>182</v>
-      </c>
       <c r="D64" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E64" s="75">
         <v>46279.125</v>
@@ -7195,13 +7230,13 @@
     </row>
     <row r="65" spans="2:43" ht="26" customHeight="1">
       <c r="B65" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="C65" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="C65" s="73" t="s">
-        <v>184</v>
-      </c>
       <c r="D65" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E65" s="75">
         <v>46280.125</v>
@@ -7254,13 +7289,13 @@
     </row>
     <row r="66" spans="2:43" ht="26" customHeight="1">
       <c r="B66" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66" s="73" t="s">
         <v>185</v>
       </c>
-      <c r="C66" s="73" t="s">
-        <v>186</v>
-      </c>
       <c r="D66" s="74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E66" s="75">
         <v>46282.125</v>
@@ -7313,13 +7348,13 @@
     </row>
     <row r="67" spans="2:43" ht="26" customHeight="1">
       <c r="B67" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="C67" s="73" t="s">
         <v>187</v>
       </c>
-      <c r="C67" s="73" t="s">
+      <c r="D67" s="74" t="s">
         <v>188</v>
-      </c>
-      <c r="D67" s="74" t="s">
-        <v>189</v>
       </c>
       <c r="E67" s="75">
         <v>46283.125</v>
@@ -7371,655 +7406,658 @@
       <c r="AQ67" s="133"/>
     </row>
     <row r="69" spans="2:43" ht="22" customHeight="1">
-      <c r="B69" s="143" t="s">
+      <c r="B69" s="172" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="F69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="G69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="H69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="I69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="J69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="K69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="L69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="M69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="N69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="O69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="P69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="R69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="S69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="T69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="U69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="V69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="W69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="X69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="Z69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AA69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AD69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AF69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AG69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AH69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AI69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AJ69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AK69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AL69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AN69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AO69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AP69" s="173" t="s">
+        <v>189</v>
+      </c>
+      <c r="AQ69" s="174" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="70" spans="2:43" ht="26" customHeight="1">
+      <c r="B70" s="154" t="s">
         <v>190</v>
       </c>
-      <c r="C69" s="144" t="s">
+      <c r="C70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="D69" s="144" t="s">
+      <c r="D70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="144" t="s">
+      <c r="E70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="F69" s="144" t="s">
+      <c r="F70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="G69" s="144" t="s">
+      <c r="G70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="H69" s="144" t="s">
+      <c r="H70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="I69" s="144" t="s">
+      <c r="I70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="J69" s="144" t="s">
+      <c r="J70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="K69" s="144" t="s">
+      <c r="K70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="L69" s="144" t="s">
+      <c r="L70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="M69" s="144" t="s">
+      <c r="M70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="N69" s="144" t="s">
+      <c r="N70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="O69" s="144" t="s">
+      <c r="O70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="P69" s="144" t="s">
+      <c r="P70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="Q69" s="144" t="s">
+      <c r="Q70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="R69" s="144" t="s">
+      <c r="R70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="S69" s="144" t="s">
+      <c r="S70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="T69" s="144" t="s">
+      <c r="T70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="U69" s="144" t="s">
+      <c r="U70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="V69" s="144" t="s">
+      <c r="V70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="W69" s="144" t="s">
+      <c r="W70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="X69" s="144" t="s">
+      <c r="X70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="Y69" s="144" t="s">
+      <c r="Y70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="Z69" s="144" t="s">
+      <c r="Z70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AA69" s="144" t="s">
+      <c r="AA70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AB69" s="144" t="s">
+      <c r="AB70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AC69" s="144" t="s">
+      <c r="AC70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AD69" s="144" t="s">
+      <c r="AD70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AE69" s="144" t="s">
+      <c r="AE70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AF69" s="144" t="s">
+      <c r="AF70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AG69" s="144" t="s">
+      <c r="AG70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AH69" s="144" t="s">
+      <c r="AH70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AI69" s="144" t="s">
+      <c r="AI70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AJ69" s="144" t="s">
+      <c r="AJ70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AK69" s="144" t="s">
+      <c r="AK70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AL69" s="144" t="s">
+      <c r="AL70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AM69" s="144" t="s">
+      <c r="AM70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AN69" s="144" t="s">
+      <c r="AN70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AO69" s="144" t="s">
+      <c r="AO70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AP69" s="144" t="s">
+      <c r="AP70" s="155" t="s">
         <v>190</v>
       </c>
-      <c r="AQ69" s="145" t="s">
+      <c r="AQ70" s="156" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="70" spans="2:43" ht="26" customHeight="1">
-      <c r="B70" s="146" t="s">
+    <row r="71" spans="2:43" ht="26" customHeight="1">
+      <c r="B71" s="154" t="s">
         <v>191</v>
       </c>
-      <c r="C70" s="147" t="s">
+      <c r="C71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="D70" s="147" t="s">
+      <c r="D71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="E70" s="147" t="s">
+      <c r="E71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="F70" s="147" t="s">
+      <c r="F71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="G70" s="147" t="s">
+      <c r="G71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="H70" s="147" t="s">
+      <c r="H71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="I70" s="147" t="s">
+      <c r="I71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="J70" s="147" t="s">
+      <c r="J71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="K70" s="147" t="s">
+      <c r="K71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="L70" s="147" t="s">
+      <c r="L71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="M70" s="147" t="s">
+      <c r="M71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="N70" s="147" t="s">
+      <c r="N71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="O70" s="147" t="s">
+      <c r="O71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="P70" s="147" t="s">
+      <c r="P71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="Q70" s="147" t="s">
+      <c r="Q71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="R70" s="147" t="s">
+      <c r="R71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="S70" s="147" t="s">
+      <c r="S71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="T70" s="147" t="s">
+      <c r="T71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="U70" s="147" t="s">
+      <c r="U71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="V70" s="147" t="s">
+      <c r="V71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="W70" s="147" t="s">
+      <c r="W71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="X70" s="147" t="s">
+      <c r="X71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="Y70" s="147" t="s">
+      <c r="Y71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="Z70" s="147" t="s">
+      <c r="Z71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AA70" s="147" t="s">
+      <c r="AA71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AB70" s="147" t="s">
+      <c r="AB71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AC70" s="147" t="s">
+      <c r="AC71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AD70" s="147" t="s">
+      <c r="AD71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AE70" s="147" t="s">
+      <c r="AE71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AF70" s="147" t="s">
+      <c r="AF71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AG70" s="147" t="s">
+      <c r="AG71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AH70" s="147" t="s">
+      <c r="AH71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AI70" s="147" t="s">
+      <c r="AI71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AJ70" s="147" t="s">
+      <c r="AJ71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AK70" s="147" t="s">
+      <c r="AK71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AL70" s="147" t="s">
+      <c r="AL71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AM70" s="147" t="s">
+      <c r="AM71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AN70" s="147" t="s">
+      <c r="AN71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AO70" s="147" t="s">
+      <c r="AO71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AP70" s="147" t="s">
+      <c r="AP71" s="155" t="s">
         <v>191</v>
       </c>
-      <c r="AQ70" s="148" t="s">
+      <c r="AQ71" s="156" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="2:43" ht="26" customHeight="1">
-      <c r="B71" s="146" t="s">
+    <row r="72" spans="2:43" ht="26" customHeight="1">
+      <c r="B72" s="175" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="C71" s="147" t="s">
+      <c r="D72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="147" t="s">
+      <c r="E72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="E71" s="147" t="s">
+      <c r="F72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="F71" s="147" t="s">
+      <c r="G72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="G71" s="147" t="s">
+      <c r="H72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="H71" s="147" t="s">
+      <c r="I72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="I71" s="147" t="s">
+      <c r="J72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="J71" s="147" t="s">
+      <c r="K72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="K71" s="147" t="s">
+      <c r="L72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="L71" s="147" t="s">
+      <c r="M72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="M71" s="147" t="s">
+      <c r="N72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="N71" s="147" t="s">
+      <c r="O72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="O71" s="147" t="s">
+      <c r="P72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="P71" s="147" t="s">
+      <c r="Q72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="Q71" s="147" t="s">
+      <c r="R72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="R71" s="147" t="s">
+      <c r="S72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="S71" s="147" t="s">
+      <c r="T72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="T71" s="147" t="s">
+      <c r="U72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="U71" s="147" t="s">
+      <c r="V72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="V71" s="147" t="s">
+      <c r="W72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="W71" s="147" t="s">
+      <c r="X72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="X71" s="147" t="s">
+      <c r="Y72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="Y71" s="147" t="s">
+      <c r="Z72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="Z71" s="147" t="s">
+      <c r="AA72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AA71" s="147" t="s">
+      <c r="AB72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AB71" s="147" t="s">
+      <c r="AC72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AC71" s="147" t="s">
+      <c r="AD72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AD71" s="147" t="s">
+      <c r="AE72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AE71" s="147" t="s">
+      <c r="AF72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AF71" s="147" t="s">
+      <c r="AG72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AG71" s="147" t="s">
+      <c r="AH72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AH71" s="147" t="s">
+      <c r="AI72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AI71" s="147" t="s">
+      <c r="AJ72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AJ71" s="147" t="s">
+      <c r="AK72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AK71" s="147" t="s">
+      <c r="AL72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AL71" s="147" t="s">
+      <c r="AM72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AM71" s="147" t="s">
+      <c r="AN72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AN71" s="147" t="s">
+      <c r="AO72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AO71" s="147" t="s">
+      <c r="AP72" s="155" t="s">
         <v>192</v>
       </c>
-      <c r="AP71" s="147" t="s">
+      <c r="AQ72" s="156" t="s">
         <v>192</v>
       </c>
-      <c r="AQ71" s="148" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="72" spans="2:43" ht="26" customHeight="1">
-      <c r="B72" s="149" t="s">
-        <v>196</v>
-      </c>
-      <c r="C72" s="147" t="s">
+    </row>
+    <row r="73" spans="2:43" ht="26" customHeight="1">
+      <c r="B73" s="154" t="s">
         <v>193</v>
       </c>
-      <c r="D72" s="147" t="s">
+      <c r="C73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="E72" s="147" t="s">
+      <c r="D73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="F72" s="147" t="s">
+      <c r="E73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="G72" s="147" t="s">
+      <c r="F73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="H72" s="147" t="s">
+      <c r="G73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="I72" s="147" t="s">
+      <c r="H73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="J72" s="147" t="s">
+      <c r="I73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="K72" s="147" t="s">
+      <c r="J73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="L72" s="147" t="s">
+      <c r="K73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="M72" s="147" t="s">
+      <c r="L73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="N72" s="147" t="s">
+      <c r="M73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="O72" s="147" t="s">
+      <c r="N73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="P72" s="147" t="s">
+      <c r="O73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="Q72" s="147" t="s">
+      <c r="P73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="R72" s="147" t="s">
+      <c r="Q73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="S72" s="147" t="s">
+      <c r="R73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="T72" s="147" t="s">
+      <c r="S73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="U72" s="147" t="s">
+      <c r="T73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="V72" s="147" t="s">
+      <c r="U73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="W72" s="147" t="s">
+      <c r="V73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="X72" s="147" t="s">
+      <c r="W73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="Y72" s="147" t="s">
+      <c r="X73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="Z72" s="147" t="s">
+      <c r="Y73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AA72" s="147" t="s">
+      <c r="Z73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AB72" s="147" t="s">
+      <c r="AA73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AC72" s="147" t="s">
+      <c r="AB73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AD72" s="147" t="s">
+      <c r="AC73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AE72" s="147" t="s">
+      <c r="AD73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AF72" s="147" t="s">
+      <c r="AE73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AG72" s="147" t="s">
+      <c r="AF73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AH72" s="147" t="s">
+      <c r="AG73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AI72" s="147" t="s">
+      <c r="AH73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AJ72" s="147" t="s">
+      <c r="AI73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AK72" s="147" t="s">
+      <c r="AJ73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AL72" s="147" t="s">
+      <c r="AK73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AM72" s="147" t="s">
+      <c r="AL73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AN72" s="147" t="s">
+      <c r="AM73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AO72" s="147" t="s">
+      <c r="AN73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AP72" s="147" t="s">
+      <c r="AO73" s="155" t="s">
         <v>193</v>
       </c>
-      <c r="AQ72" s="148" t="s">
+      <c r="AP73" s="155" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="73" spans="2:43" ht="26" customHeight="1">
-      <c r="B73" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="C73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="D73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="E73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="F73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="G73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="H73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="I73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="J73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="K73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="L73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="M73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="N73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="O73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="P73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="R73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="S73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="T73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="U73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="V73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="W73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="X73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="Y73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AA73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AC73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AD73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AE73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AF73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AG73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AH73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AJ73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AK73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AL73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AM73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AN73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AO73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AP73" s="147" t="s">
-        <v>194</v>
-      </c>
-      <c r="AQ73" s="148" t="s">
-        <v>194</v>
+      <c r="AQ73" s="156" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="O2:AG2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="H4:O4"/>
-    <mergeCell ref="P4:AG4"/>
-    <mergeCell ref="A3:XFD3"/>
+    <mergeCell ref="P5:AG5"/>
+    <mergeCell ref="B69:AQ69"/>
+    <mergeCell ref="B70:AQ70"/>
+    <mergeCell ref="B71:AQ71"/>
+    <mergeCell ref="B72:AQ72"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="I8:M8"/>
+    <mergeCell ref="N8:W8"/>
+    <mergeCell ref="X8:AL8"/>
+    <mergeCell ref="H5:O5"/>
     <mergeCell ref="B73:AQ73"/>
     <mergeCell ref="AM8:AQ8"/>
     <mergeCell ref="I9:M9"/>
@@ -8036,17 +8074,14 @@
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="G8:G10"/>
     <mergeCell ref="H8:H10"/>
-    <mergeCell ref="P5:AG5"/>
-    <mergeCell ref="B69:AQ69"/>
-    <mergeCell ref="B70:AQ70"/>
-    <mergeCell ref="B71:AQ71"/>
-    <mergeCell ref="B72:AQ72"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="I8:M8"/>
-    <mergeCell ref="N8:W8"/>
-    <mergeCell ref="X8:AL8"/>
-    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="I2:N2"/>
+    <mergeCell ref="O2:AG2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="H4:O4"/>
+    <mergeCell ref="P4:AG4"/>
+    <mergeCell ref="A3:XFD3"/>
   </mergeCells>
   <phoneticPr fontId="25" type="noConversion"/>
   <conditionalFormatting sqref="H11:H67">
@@ -8130,876 +8165,876 @@
   <sheetData>
     <row r="1" spans="1:7" ht="43" customHeight="1">
       <c r="A1" s="189" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B1" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D1" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E1" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F1" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G1" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19" customHeight="1">
       <c r="A2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G2" s="191" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1">
       <c r="A4" s="138" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="138" t="s">
         <v>199</v>
       </c>
-      <c r="B4" s="138" t="s">
+      <c r="C4" s="138" t="s">
         <v>200</v>
       </c>
-      <c r="C4" s="138" t="s">
+      <c r="D4" s="138" t="s">
         <v>201</v>
       </c>
-      <c r="D4" s="138" t="s">
+      <c r="E4" s="138" t="s">
         <v>202</v>
       </c>
-      <c r="E4" s="138" t="s">
+      <c r="F4" s="138" t="s">
         <v>203</v>
       </c>
-      <c r="F4" s="138" t="s">
+      <c r="G4" s="138" t="s">
         <v>204</v>
-      </c>
-      <c r="G4" s="138" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="35" customHeight="1">
       <c r="A5" s="139" t="s">
+        <v>205</v>
+      </c>
+      <c r="B5" s="139" t="s">
         <v>206</v>
       </c>
-      <c r="B5" s="139" t="s">
+      <c r="C5" s="139" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="139" t="s">
+      <c r="D5" s="139" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="139" t="s">
+      <c r="E5" s="139" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="139" t="s">
+      <c r="F5" s="139" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="139" t="s">
+      <c r="G5" s="140" t="s">
         <v>211</v>
-      </c>
-      <c r="G5" s="140" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="35" customHeight="1">
       <c r="A6" s="139" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="139" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="139" t="s">
+      <c r="C6" s="139" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="139" t="s">
+      <c r="D6" s="139" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="139" t="s">
+      <c r="E6" s="139" t="s">
         <v>216</v>
       </c>
-      <c r="E6" s="139" t="s">
+      <c r="F6" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G6" s="140" t="s">
         <v>217</v>
-      </c>
-      <c r="F6" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G6" s="140" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="35" customHeight="1">
       <c r="A7" s="139" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="139" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="139" t="s">
+      <c r="C7" s="139" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="139" t="s">
+      <c r="D7" s="139" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="139" t="s">
+      <c r="E7" s="139" t="s">
         <v>222</v>
       </c>
-      <c r="E7" s="139" t="s">
+      <c r="F7" s="139" t="s">
         <v>223</v>
       </c>
-      <c r="F7" s="139" t="s">
+      <c r="G7" s="140" t="s">
         <v>224</v>
-      </c>
-      <c r="G7" s="140" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="35" customHeight="1">
       <c r="A8" s="139" t="s">
+        <v>225</v>
+      </c>
+      <c r="B8" s="139" t="s">
         <v>226</v>
       </c>
-      <c r="B8" s="139" t="s">
+      <c r="C8" s="139" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="139" t="s">
+      <c r="D8" s="139" t="s">
         <v>228</v>
       </c>
-      <c r="D8" s="139" t="s">
+      <c r="E8" s="139" t="s">
         <v>229</v>
       </c>
-      <c r="E8" s="139" t="s">
+      <c r="F8" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G8" s="140" t="s">
         <v>230</v>
-      </c>
-      <c r="F8" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G8" s="140" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="35" customHeight="1">
       <c r="A9" s="139" t="s">
+        <v>231</v>
+      </c>
+      <c r="B9" s="139" t="s">
         <v>232</v>
       </c>
-      <c r="B9" s="139" t="s">
+      <c r="C9" s="139" t="s">
         <v>233</v>
       </c>
-      <c r="C9" s="139" t="s">
+      <c r="D9" s="139" t="s">
         <v>234</v>
       </c>
-      <c r="D9" s="139" t="s">
+      <c r="E9" s="139" t="s">
         <v>235</v>
       </c>
-      <c r="E9" s="139" t="s">
+      <c r="F9" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="140" t="s">
         <v>236</v>
-      </c>
-      <c r="F9" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G9" s="140" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="35" customHeight="1">
       <c r="A10" s="139" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="139" t="s">
         <v>238</v>
       </c>
-      <c r="B10" s="139" t="s">
+      <c r="C10" s="139" t="s">
         <v>239</v>
       </c>
-      <c r="C10" s="139" t="s">
+      <c r="D10" s="139" t="s">
         <v>240</v>
       </c>
-      <c r="D10" s="139" t="s">
+      <c r="E10" s="139" t="s">
         <v>241</v>
       </c>
-      <c r="E10" s="139" t="s">
+      <c r="F10" s="139" t="s">
         <v>242</v>
       </c>
-      <c r="F10" s="139" t="s">
+      <c r="G10" s="140" t="s">
         <v>243</v>
-      </c>
-      <c r="G10" s="140" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="35" customHeight="1">
       <c r="A11" s="139" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="139" t="s">
         <v>245</v>
       </c>
-      <c r="B11" s="139" t="s">
+      <c r="C11" s="139" t="s">
         <v>246</v>
       </c>
-      <c r="C11" s="139" t="s">
+      <c r="D11" s="139" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="139" t="s">
+      <c r="E11" s="139" t="s">
         <v>248</v>
       </c>
-      <c r="E11" s="139" t="s">
+      <c r="F11" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="140" t="s">
         <v>249</v>
-      </c>
-      <c r="F11" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G11" s="140" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="35" customHeight="1">
       <c r="A12" s="139" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="139" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="139" t="s">
+      <c r="C12" s="139" t="s">
         <v>252</v>
       </c>
-      <c r="C12" s="139" t="s">
+      <c r="D12" s="139" t="s">
         <v>253</v>
       </c>
-      <c r="D12" s="139" t="s">
+      <c r="E12" s="139" t="s">
         <v>254</v>
       </c>
-      <c r="E12" s="139" t="s">
+      <c r="F12" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="140" t="s">
         <v>255</v>
-      </c>
-      <c r="F12" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G12" s="140" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="35" customHeight="1">
       <c r="A13" s="139" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="139" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="139" t="s">
+      <c r="C13" s="139" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="139" t="s">
+      <c r="D13" s="139" t="s">
         <v>259</v>
       </c>
-      <c r="D13" s="139" t="s">
+      <c r="E13" s="139" t="s">
         <v>260</v>
       </c>
-      <c r="E13" s="139" t="s">
+      <c r="F13" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G13" s="140" t="s">
         <v>261</v>
-      </c>
-      <c r="F13" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G13" s="140" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="35" customHeight="1">
       <c r="A14" s="139" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="139" t="s">
         <v>263</v>
       </c>
-      <c r="B14" s="139" t="s">
+      <c r="C14" s="139" t="s">
         <v>264</v>
       </c>
-      <c r="C14" s="139" t="s">
+      <c r="D14" s="139" t="s">
         <v>265</v>
       </c>
-      <c r="D14" s="139" t="s">
+      <c r="E14" s="139" t="s">
         <v>266</v>
       </c>
-      <c r="E14" s="139" t="s">
+      <c r="F14" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="140" t="s">
         <v>267</v>
-      </c>
-      <c r="F14" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G14" s="140" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="35" customHeight="1">
       <c r="A15" s="139" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="139" t="s">
         <v>269</v>
       </c>
-      <c r="B15" s="139" t="s">
+      <c r="C15" s="139" t="s">
         <v>270</v>
       </c>
-      <c r="C15" s="139" t="s">
+      <c r="D15" s="139" t="s">
         <v>271</v>
       </c>
-      <c r="D15" s="139" t="s">
+      <c r="E15" s="139" t="s">
         <v>272</v>
       </c>
-      <c r="E15" s="139" t="s">
+      <c r="F15" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G15" s="140" t="s">
         <v>273</v>
-      </c>
-      <c r="F15" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G15" s="140" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="35" customHeight="1">
       <c r="A16" s="139" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="139" t="s">
         <v>275</v>
       </c>
-      <c r="B16" s="139" t="s">
+      <c r="C16" s="139" t="s">
         <v>276</v>
       </c>
-      <c r="C16" s="139" t="s">
+      <c r="D16" s="139" t="s">
         <v>277</v>
       </c>
-      <c r="D16" s="139" t="s">
+      <c r="E16" s="139" t="s">
         <v>278</v>
       </c>
-      <c r="E16" s="139" t="s">
+      <c r="F16" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G16" s="140" t="s">
         <v>279</v>
-      </c>
-      <c r="F16" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G16" s="140" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="35" customHeight="1">
       <c r="A17" s="139" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" s="139" t="s">
         <v>281</v>
       </c>
-      <c r="B17" s="139" t="s">
+      <c r="C17" s="139" t="s">
         <v>282</v>
       </c>
-      <c r="C17" s="139" t="s">
+      <c r="D17" s="139" t="s">
         <v>283</v>
       </c>
-      <c r="D17" s="139" t="s">
+      <c r="E17" s="139" t="s">
         <v>284</v>
       </c>
-      <c r="E17" s="139" t="s">
+      <c r="F17" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G17" s="140" t="s">
         <v>285</v>
-      </c>
-      <c r="F17" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G17" s="140" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="35" customHeight="1">
       <c r="A18" s="139" t="s">
+        <v>286</v>
+      </c>
+      <c r="B18" s="139" t="s">
         <v>287</v>
       </c>
-      <c r="B18" s="139" t="s">
+      <c r="C18" s="139" t="s">
         <v>288</v>
       </c>
-      <c r="C18" s="139" t="s">
+      <c r="D18" s="139" t="s">
         <v>289</v>
       </c>
-      <c r="D18" s="139" t="s">
+      <c r="E18" s="139" t="s">
         <v>290</v>
       </c>
-      <c r="E18" s="139" t="s">
+      <c r="F18" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G18" s="140" t="s">
         <v>291</v>
-      </c>
-      <c r="F18" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G18" s="140" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="35" customHeight="1">
       <c r="A19" s="139" t="s">
+        <v>292</v>
+      </c>
+      <c r="B19" s="139" t="s">
         <v>293</v>
       </c>
-      <c r="B19" s="139" t="s">
+      <c r="C19" s="139" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="139" t="s">
         <v>294</v>
       </c>
-      <c r="C19" s="139" t="s">
-        <v>240</v>
-      </c>
-      <c r="D19" s="139" t="s">
+      <c r="E19" s="139" t="s">
         <v>295</v>
       </c>
-      <c r="E19" s="139" t="s">
+      <c r="F19" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G19" s="140" t="s">
         <v>296</v>
-      </c>
-      <c r="F19" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G19" s="140" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="35" customHeight="1">
       <c r="A20" s="139" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="139" t="s">
         <v>298</v>
       </c>
-      <c r="B20" s="139" t="s">
+      <c r="C20" s="139" t="s">
+        <v>288</v>
+      </c>
+      <c r="D20" s="139" t="s">
         <v>299</v>
       </c>
-      <c r="C20" s="139" t="s">
-        <v>289</v>
-      </c>
-      <c r="D20" s="139" t="s">
+      <c r="E20" s="139" t="s">
         <v>300</v>
       </c>
-      <c r="E20" s="139" t="s">
+      <c r="F20" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G20" s="140" t="s">
         <v>301</v>
-      </c>
-      <c r="F20" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G20" s="140" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="35" customHeight="1">
       <c r="A21" s="139" t="s">
+        <v>302</v>
+      </c>
+      <c r="B21" s="139" t="s">
         <v>303</v>
       </c>
-      <c r="B21" s="139" t="s">
+      <c r="C21" s="139" t="s">
         <v>304</v>
       </c>
-      <c r="C21" s="139" t="s">
+      <c r="D21" s="139" t="s">
         <v>305</v>
       </c>
-      <c r="D21" s="139" t="s">
+      <c r="E21" s="139" t="s">
         <v>306</v>
       </c>
-      <c r="E21" s="139" t="s">
+      <c r="F21" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G21" s="140" t="s">
         <v>307</v>
-      </c>
-      <c r="F21" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G21" s="140" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="35" customHeight="1">
       <c r="A22" s="139" t="s">
+        <v>308</v>
+      </c>
+      <c r="B22" s="139" t="s">
         <v>309</v>
       </c>
-      <c r="B22" s="139" t="s">
+      <c r="C22" s="139" t="s">
+        <v>233</v>
+      </c>
+      <c r="D22" s="139" t="s">
         <v>310</v>
       </c>
-      <c r="C22" s="139" t="s">
-        <v>234</v>
-      </c>
-      <c r="D22" s="139" t="s">
+      <c r="E22" s="139" t="s">
         <v>311</v>
       </c>
-      <c r="E22" s="139" t="s">
+      <c r="F22" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G22" s="140" t="s">
         <v>312</v>
-      </c>
-      <c r="F22" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G22" s="140" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="35" customHeight="1">
       <c r="A23" s="139" t="s">
+        <v>313</v>
+      </c>
+      <c r="B23" s="139" t="s">
         <v>314</v>
       </c>
-      <c r="B23" s="139" t="s">
+      <c r="C23" s="139" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="139" t="s">
         <v>315</v>
       </c>
-      <c r="C23" s="139" t="s">
-        <v>234</v>
-      </c>
-      <c r="D23" s="139" t="s">
+      <c r="E23" s="139" t="s">
         <v>316</v>
       </c>
-      <c r="E23" s="139" t="s">
+      <c r="F23" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" s="140" t="s">
         <v>317</v>
-      </c>
-      <c r="F23" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G23" s="140" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="35" customHeight="1">
       <c r="A24" s="139" t="s">
+        <v>318</v>
+      </c>
+      <c r="B24" s="139" t="s">
         <v>319</v>
       </c>
-      <c r="B24" s="139" t="s">
+      <c r="C24" s="139" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" s="139" t="s">
         <v>320</v>
       </c>
-      <c r="C24" s="139" t="s">
-        <v>240</v>
-      </c>
-      <c r="D24" s="139" t="s">
+      <c r="E24" s="139" t="s">
         <v>321</v>
       </c>
-      <c r="E24" s="139" t="s">
+      <c r="F24" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G24" s="140" t="s">
         <v>322</v>
-      </c>
-      <c r="F24" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G24" s="140" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="35" customHeight="1">
       <c r="A25" s="139" t="s">
+        <v>323</v>
+      </c>
+      <c r="B25" s="139" t="s">
         <v>324</v>
       </c>
-      <c r="B25" s="139" t="s">
+      <c r="C25" s="139" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="139" t="s">
+      <c r="D25" s="139" t="s">
         <v>326</v>
       </c>
-      <c r="D25" s="139" t="s">
+      <c r="E25" s="139" t="s">
         <v>327</v>
       </c>
-      <c r="E25" s="139" t="s">
+      <c r="F25" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G25" s="140" t="s">
         <v>328</v>
-      </c>
-      <c r="F25" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G25" s="140" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="35" customHeight="1">
       <c r="A26" s="139" t="s">
+        <v>329</v>
+      </c>
+      <c r="B26" s="139" t="s">
         <v>330</v>
       </c>
-      <c r="B26" s="139" t="s">
+      <c r="C26" s="139" t="s">
+        <v>325</v>
+      </c>
+      <c r="D26" s="139" t="s">
         <v>331</v>
       </c>
-      <c r="C26" s="139" t="s">
-        <v>326</v>
-      </c>
-      <c r="D26" s="139" t="s">
+      <c r="E26" s="139" t="s">
         <v>332</v>
       </c>
-      <c r="E26" s="139" t="s">
+      <c r="F26" s="139" t="s">
+        <v>210</v>
+      </c>
+      <c r="G26" s="140" t="s">
         <v>333</v>
-      </c>
-      <c r="F26" s="139" t="s">
-        <v>211</v>
-      </c>
-      <c r="G26" s="140" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="35" customHeight="1">
       <c r="A27" s="139" t="s">
+        <v>334</v>
+      </c>
+      <c r="B27" s="139" t="s">
         <v>335</v>
       </c>
-      <c r="B27" s="139" t="s">
+      <c r="C27" s="139" t="s">
         <v>336</v>
       </c>
-      <c r="C27" s="139" t="s">
+      <c r="D27" s="139" t="s">
         <v>337</v>
       </c>
-      <c r="D27" s="139" t="s">
+      <c r="E27" s="139" t="s">
         <v>338</v>
       </c>
-      <c r="E27" s="139" t="s">
+      <c r="F27" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G27" s="140" t="s">
         <v>339</v>
-      </c>
-      <c r="F27" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G27" s="140" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="35" customHeight="1">
       <c r="A28" s="139" t="s">
+        <v>340</v>
+      </c>
+      <c r="B28" s="139" t="s">
         <v>341</v>
       </c>
-      <c r="B28" s="139" t="s">
+      <c r="C28" s="139" t="s">
         <v>342</v>
       </c>
-      <c r="C28" s="139" t="s">
+      <c r="D28" s="139" t="s">
         <v>343</v>
       </c>
-      <c r="D28" s="139" t="s">
+      <c r="E28" s="139" t="s">
         <v>344</v>
       </c>
-      <c r="E28" s="139" t="s">
+      <c r="F28" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="G28" s="140" t="s">
         <v>345</v>
-      </c>
-      <c r="F28" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="G28" s="140" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="35" customHeight="1">
       <c r="A29" s="139" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" s="139" t="s">
         <v>347</v>
       </c>
-      <c r="B29" s="139" t="s">
+      <c r="C29" s="139" t="s">
         <v>348</v>
       </c>
-      <c r="C29" s="139" t="s">
+      <c r="D29" s="139" t="s">
         <v>349</v>
       </c>
-      <c r="D29" s="139" t="s">
+      <c r="E29" s="139" t="s">
         <v>350</v>
       </c>
-      <c r="E29" s="139" t="s">
+      <c r="F29" s="139" t="s">
         <v>351</v>
       </c>
-      <c r="F29" s="139" t="s">
+      <c r="G29" s="140" t="s">
         <v>352</v>
-      </c>
-      <c r="G29" s="140" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="35" customHeight="1">
       <c r="A30" s="139" t="s">
+        <v>353</v>
+      </c>
+      <c r="B30" s="139" t="s">
         <v>354</v>
       </c>
-      <c r="B30" s="139" t="s">
+      <c r="C30" s="139" t="s">
         <v>355</v>
       </c>
-      <c r="C30" s="139" t="s">
+      <c r="D30" s="139" t="s">
         <v>356</v>
       </c>
-      <c r="D30" s="139" t="s">
+      <c r="E30" s="139" t="s">
         <v>357</v>
       </c>
-      <c r="E30" s="139" t="s">
+      <c r="F30" s="139" t="s">
+        <v>351</v>
+      </c>
+      <c r="G30" s="140" t="s">
         <v>358</v>
-      </c>
-      <c r="F30" s="139" t="s">
-        <v>352</v>
-      </c>
-      <c r="G30" s="140" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="35" customHeight="1">
       <c r="A31" s="139" t="s">
+        <v>359</v>
+      </c>
+      <c r="B31" s="139" t="s">
         <v>360</v>
       </c>
-      <c r="B31" s="139" t="s">
+      <c r="C31" s="139" t="s">
         <v>361</v>
       </c>
-      <c r="C31" s="139" t="s">
+      <c r="D31" s="139" t="s">
         <v>362</v>
       </c>
-      <c r="D31" s="139" t="s">
+      <c r="E31" s="139" t="s">
         <v>363</v>
       </c>
-      <c r="E31" s="139" t="s">
+      <c r="F31" s="139" t="s">
+        <v>351</v>
+      </c>
+      <c r="G31" s="140" t="s">
         <v>364</v>
-      </c>
-      <c r="F31" s="139" t="s">
-        <v>352</v>
-      </c>
-      <c r="G31" s="140" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="35" customHeight="1">
       <c r="A32" s="139" t="s">
+        <v>365</v>
+      </c>
+      <c r="B32" s="139" t="s">
         <v>366</v>
       </c>
-      <c r="B32" s="139" t="s">
+      <c r="C32" s="139" t="s">
+        <v>325</v>
+      </c>
+      <c r="D32" s="139" t="s">
         <v>367</v>
       </c>
-      <c r="C32" s="139" t="s">
-        <v>326</v>
-      </c>
-      <c r="D32" s="139" t="s">
+      <c r="E32" s="139" t="s">
         <v>368</v>
       </c>
-      <c r="E32" s="139" t="s">
+      <c r="F32" s="139" t="s">
+        <v>351</v>
+      </c>
+      <c r="G32" s="140" t="s">
         <v>369</v>
-      </c>
-      <c r="F32" s="139" t="s">
-        <v>352</v>
-      </c>
-      <c r="G32" s="140" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="35" customHeight="1">
       <c r="A33" s="139" t="s">
+        <v>370</v>
+      </c>
+      <c r="B33" s="139" t="s">
         <v>371</v>
       </c>
-      <c r="B33" s="139" t="s">
+      <c r="C33" s="139" t="s">
         <v>372</v>
       </c>
-      <c r="C33" s="139" t="s">
+      <c r="D33" s="139" t="s">
         <v>373</v>
       </c>
-      <c r="D33" s="139" t="s">
+      <c r="E33" s="139" t="s">
         <v>374</v>
       </c>
-      <c r="E33" s="139" t="s">
+      <c r="F33" s="139" t="s">
         <v>375</v>
       </c>
-      <c r="F33" s="139" t="s">
+      <c r="G33" s="140" t="s">
         <v>376</v>
-      </c>
-      <c r="G33" s="140" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="35" customHeight="1">
       <c r="A34" s="139" t="s">
+        <v>377</v>
+      </c>
+      <c r="B34" s="139" t="s">
         <v>378</v>
       </c>
-      <c r="B34" s="139" t="s">
+      <c r="C34" s="139" t="s">
+        <v>288</v>
+      </c>
+      <c r="D34" s="139" t="s">
         <v>379</v>
       </c>
-      <c r="C34" s="139" t="s">
-        <v>289</v>
-      </c>
-      <c r="D34" s="139" t="s">
+      <c r="E34" s="139" t="s">
         <v>380</v>
       </c>
-      <c r="E34" s="139" t="s">
+      <c r="F34" s="139" t="s">
         <v>381</v>
       </c>
-      <c r="F34" s="139" t="s">
+      <c r="G34" s="140" t="s">
         <v>382</v>
-      </c>
-      <c r="G34" s="140" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="35" customHeight="1">
       <c r="A35" s="139" t="s">
+        <v>383</v>
+      </c>
+      <c r="B35" s="139" t="s">
         <v>384</v>
       </c>
-      <c r="B35" s="139" t="s">
+      <c r="C35" s="139" t="s">
         <v>385</v>
       </c>
-      <c r="C35" s="139" t="s">
+      <c r="D35" s="139" t="s">
         <v>386</v>
       </c>
-      <c r="D35" s="139" t="s">
+      <c r="E35" s="139" t="s">
         <v>387</v>
       </c>
-      <c r="E35" s="139" t="s">
+      <c r="F35" s="139" t="s">
+        <v>381</v>
+      </c>
+      <c r="G35" s="140" t="s">
         <v>388</v>
-      </c>
-      <c r="F35" s="139" t="s">
-        <v>382</v>
-      </c>
-      <c r="G35" s="140" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="35" customHeight="1">
       <c r="A36" s="139" t="s">
+        <v>389</v>
+      </c>
+      <c r="B36" s="139" t="s">
         <v>390</v>
       </c>
-      <c r="B36" s="139" t="s">
+      <c r="C36" s="139" t="s">
         <v>391</v>
       </c>
-      <c r="C36" s="139" t="s">
+      <c r="D36" s="139" t="s">
         <v>392</v>
       </c>
-      <c r="D36" s="139" t="s">
+      <c r="E36" s="139" t="s">
         <v>393</v>
       </c>
-      <c r="E36" s="139" t="s">
+      <c r="F36" s="139" t="s">
+        <v>381</v>
+      </c>
+      <c r="G36" s="140" t="s">
         <v>394</v>
-      </c>
-      <c r="F36" s="139" t="s">
-        <v>382</v>
-      </c>
-      <c r="G36" s="140" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="35" customHeight="1">
       <c r="A37" s="139" t="s">
+        <v>395</v>
+      </c>
+      <c r="B37" s="139" t="s">
         <v>396</v>
       </c>
-      <c r="B37" s="139" t="s">
+      <c r="C37" s="139" t="s">
+        <v>361</v>
+      </c>
+      <c r="D37" s="139" t="s">
         <v>397</v>
       </c>
-      <c r="C37" s="139" t="s">
-        <v>362</v>
-      </c>
-      <c r="D37" s="139" t="s">
+      <c r="E37" s="139" t="s">
         <v>398</v>
       </c>
-      <c r="E37" s="139" t="s">
+      <c r="F37" s="139" t="s">
+        <v>381</v>
+      </c>
+      <c r="G37" s="140" t="s">
         <v>399</v>
-      </c>
-      <c r="F37" s="139" t="s">
-        <v>382</v>
-      </c>
-      <c r="G37" s="140" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="35" customHeight="1">
       <c r="A38" s="139" t="s">
+        <v>400</v>
+      </c>
+      <c r="B38" s="139" t="s">
         <v>401</v>
       </c>
-      <c r="B38" s="139" t="s">
+      <c r="C38" s="139" t="s">
         <v>402</v>
       </c>
-      <c r="C38" s="139" t="s">
+      <c r="D38" s="139" t="s">
         <v>403</v>
       </c>
-      <c r="D38" s="139" t="s">
+      <c r="E38" s="139" t="s">
         <v>404</v>
       </c>
-      <c r="E38" s="139" t="s">
+      <c r="F38" s="139" t="s">
+        <v>381</v>
+      </c>
+      <c r="G38" s="140" t="s">
         <v>405</v>
-      </c>
-      <c r="F38" s="139" t="s">
-        <v>382</v>
-      </c>
-      <c r="G38" s="140" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="35" customHeight="1">
       <c r="A39" s="139" t="s">
+        <v>406</v>
+      </c>
+      <c r="B39" s="139" t="s">
         <v>407</v>
       </c>
-      <c r="B39" s="139" t="s">
+      <c r="C39" s="139" t="s">
         <v>408</v>
       </c>
-      <c r="C39" s="139" t="s">
+      <c r="D39" s="139" t="s">
         <v>409</v>
       </c>
-      <c r="D39" s="139" t="s">
+      <c r="E39" s="139" t="s">
         <v>410</v>
       </c>
-      <c r="E39" s="139" t="s">
+      <c r="F39" s="139" t="s">
+        <v>381</v>
+      </c>
+      <c r="G39" s="140" t="s">
         <v>411</v>
-      </c>
-      <c r="F39" s="139" t="s">
-        <v>382</v>
-      </c>
-      <c r="G39" s="140" t="s">
-        <v>412</v>
       </c>
     </row>
   </sheetData>
